--- a/grupos/6ARHV - Estadisticos 20232.xlsx
+++ b/grupos/6ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -170,18 +170,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
+    <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,46 +194,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
     <t>NOYOLA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
     <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>XIMENA</t>
@@ -744,22 +753,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -783,10 +792,10 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -795,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -821,22 +830,22 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -860,13 +869,13 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -898,22 +907,22 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -940,13 +949,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -975,22 +984,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1026,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1052,22 +1061,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1091,13 +1100,13 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1129,22 +1138,22 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1168,16 +1177,16 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1206,22 +1215,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1245,13 +1254,13 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1283,22 +1292,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1319,19 +1328,19 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1360,22 +1369,22 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1402,16 +1411,16 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1437,22 +1446,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1473,13 +1482,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1514,22 +1523,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1559,10 +1568,10 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1591,22 +1600,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1630,19 +1639,19 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1668,22 +1677,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1704,13 +1713,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>8</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1719,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1733,10 +1742,10 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1774,22 +1783,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1822,10 +1831,10 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1851,22 +1860,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1896,13 +1905,13 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1928,22 +1937,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -1964,7 +1973,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -1976,10 +1985,10 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2005,22 +2014,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2044,19 +2053,19 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2082,22 +2091,22 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2121,7 +2130,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2159,22 +2168,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2198,19 +2207,19 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2236,22 +2245,22 @@
         <v>4</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2275,16 +2284,16 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2313,22 +2322,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2352,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2390,22 +2399,22 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2426,10 +2435,10 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2467,22 +2476,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2503,22 +2512,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2544,22 +2553,22 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2580,10 +2589,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2621,22 +2630,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2657,19 +2666,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>9</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>5</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2808,40 +2817,40 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="I4">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J4">
-        <v>88.5</v>
+        <v>82.7</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
-        <v>88.5</v>
+        <v>82.7</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2867,40 +2876,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I5">
+        <v>97.5</v>
+      </c>
+      <c r="J5">
+        <v>86.5</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>94.2</v>
+      </c>
+      <c r="M5">
+        <v>94.5</v>
+      </c>
+      <c r="N5">
         <v>95</v>
       </c>
-      <c r="J5">
-        <v>96.2</v>
-      </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
-      <c r="L5">
-        <v>96.2</v>
-      </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>90</v>
-      </c>
       <c r="O5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P5">
-        <v>96.2</v>
+        <v>86.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>96.2</v>
+        <v>94.2</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2932,7 +2941,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -2941,7 +2950,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -2950,7 +2959,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2959,7 +2968,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3000,7 +3009,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3018,7 +3027,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3050,7 +3059,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3068,7 +3077,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3103,40 +3112,40 @@
         <v>86.7</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="M9">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="S9">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3165,37 +3174,37 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3221,40 +3230,40 @@
         <v>96.7</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I11">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J11">
-        <v>88.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="M11">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O11">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="P11">
-        <v>88.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="S11">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3280,40 +3289,40 @@
         <v>86.7</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J12">
-        <v>84.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>88.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M12">
-        <v>86.7</v>
+        <v>87.3</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O12">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="P12">
-        <v>84.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>88.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="S12">
-        <v>86.7</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3339,13 +3348,13 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3354,16 +3363,16 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3372,7 +3381,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3398,40 +3407,40 @@
         <v>96.7</v>
       </c>
       <c r="H14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="I14">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J14">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M14">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P14">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S14">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3457,40 +3466,40 @@
         <v>93.3</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I15">
         <v>90</v>
       </c>
       <c r="J15">
-        <v>84.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>88.5</v>
+        <v>86.5</v>
       </c>
       <c r="M15">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O15">
         <v>90</v>
       </c>
       <c r="P15">
-        <v>84.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>88.5</v>
+        <v>86.5</v>
       </c>
       <c r="S15">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3516,13 +3525,13 @@
         <v>93.3</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -3531,16 +3540,16 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3549,7 +3558,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3563,13 +3572,13 @@
         <v>50</v>
       </c>
       <c r="H17">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="I17">
         <v>50</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="O17">
         <v>50</v>
@@ -3598,13 +3607,13 @@
         <v>93.3</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J18">
-        <v>96.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -3613,16 +3622,16 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P18">
-        <v>96.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3631,7 +3640,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>93.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3669,10 +3678,10 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M19">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -3687,10 +3696,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3716,40 +3725,40 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J20">
+        <v>94.2</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>96.2</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
       <c r="M20">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P20">
+        <v>94.2</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>96.2</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
-        <v>100</v>
-      </c>
       <c r="S20">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3775,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -3793,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3837,37 +3846,37 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3893,40 +3902,40 @@
         <v>96.7</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J23">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>96.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M23">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P23">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3952,13 +3961,13 @@
         <v>86.7</v>
       </c>
       <c r="H24">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="I24">
         <v>90</v>
       </c>
       <c r="J24">
-        <v>88.5</v>
+        <v>80.8</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -3967,16 +3976,16 @@
         <v>88.5</v>
       </c>
       <c r="M24">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N24">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="O24">
         <v>90</v>
       </c>
       <c r="P24">
-        <v>88.5</v>
+        <v>80.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -3985,7 +3994,7 @@
         <v>88.5</v>
       </c>
       <c r="S24">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4011,40 +4020,40 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J25">
-        <v>96.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>96.2</v>
+        <v>94.2</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P25">
-        <v>96.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>96.2</v>
+        <v>94.2</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4073,10 +4082,10 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J26">
-        <v>96.2</v>
+        <v>88.5</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4085,16 +4094,16 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
-        <v>96.2</v>
+        <v>88.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4103,7 +4112,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4135,7 +4144,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4153,7 +4162,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4188,7 +4197,7 @@
         <v>96.7</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="I28">
         <v>85</v>
@@ -4200,13 +4209,13 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>88.5</v>
+        <v>78.8</v>
       </c>
       <c r="M28">
-        <v>96.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N28">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="O28">
         <v>85</v>
@@ -4218,10 +4227,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>88.5</v>
+        <v>78.8</v>
       </c>
       <c r="S28">
-        <v>96.7</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4247,40 +4256,40 @@
         <v>96.7</v>
       </c>
       <c r="H29">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="M29">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N29">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="S29">
-        <v>96.7</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4337,28 +4346,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>84</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>16</v>
+        <v>26.9</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4369,7 +4378,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4378,19 +4387,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4401,28 +4410,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4436,25 +4445,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>25</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4468,25 +4477,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4497,28 +4506,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="G7" s="2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4568,7 +4577,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4600,22 +4609,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920132</v>
+        <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4623,19 +4632,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920132</v>
+        <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -4646,19 +4655,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>50</v>
@@ -4669,19 +4678,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920041</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
@@ -4692,19 +4701,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920057</v>
+        <v>21330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>50</v>
@@ -4715,24 +4724,116 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920065</v>
+        <v>21330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
         <v>52</v>
       </c>
-      <c r="G7">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920041</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920065</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHV - Estadisticos 20232.xlsx
+++ b/grupos/6ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -170,18 +170,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,58 +194,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
   </si>
   <si>
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
+    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -771,40 +744,40 @@
         <v>4</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -848,22 +821,22 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -925,22 +898,22 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1002,22 +975,22 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1079,40 +1052,40 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1156,40 +1129,40 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1233,22 +1206,22 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1257,10 +1230,10 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1310,31 +1283,31 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1387,22 +1360,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1411,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1420,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1464,25 +1437,25 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1497,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1541,25 +1514,25 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1571,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1618,28 +1591,28 @@
         <v>4</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1651,7 +1624,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1695,25 +1668,25 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1748,10 +1721,10 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1801,28 +1774,28 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -1834,7 +1807,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1878,28 +1851,28 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -1955,22 +1928,22 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -1982,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2032,22 +2005,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2109,31 +2082,31 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2186,22 +2159,22 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2219,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2263,40 +2236,40 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2340,22 +2313,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2373,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2417,34 +2390,34 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2494,25 +2467,25 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2571,40 +2544,40 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>5</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2648,25 +2621,25 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2675,13 +2648,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2835,22 +2808,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N4">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="O4">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P4">
-        <v>82.7</v>
+        <v>83.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>84.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="S4">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2894,22 +2867,22 @@
         <v>94.5</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P5">
-        <v>86.5</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>94.2</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2959,7 +2932,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2968,7 +2941,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3027,7 +3000,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3077,13 +3050,13 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3130,22 +3103,22 @@
         <v>92.7</v>
       </c>
       <c r="N9">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O9">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="P9">
+        <v>86.3</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>95</v>
       </c>
-      <c r="P9">
-        <v>86.5</v>
-      </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
-        <v>92.3</v>
-      </c>
       <c r="S9">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3192,19 +3165,19 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="S10">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3248,22 +3221,22 @@
         <v>92.7</v>
       </c>
       <c r="N11">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O11">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P11">
-        <v>76.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="S11">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3307,22 +3280,22 @@
         <v>87.3</v>
       </c>
       <c r="N12">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="O12">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="P12">
-        <v>80.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>90.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3366,13 +3339,13 @@
         <v>98.2</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P13">
-        <v>94.2</v>
+        <v>96.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3381,7 +3354,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3425,22 +3398,22 @@
         <v>94.5</v>
       </c>
       <c r="N14">
+        <v>94.5</v>
+      </c>
+      <c r="O14">
+        <v>95.3</v>
+      </c>
+      <c r="P14">
         <v>93.8</v>
       </c>
-      <c r="O14">
-        <v>92.5</v>
-      </c>
-      <c r="P14">
-        <v>92.3</v>
-      </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3484,22 +3457,22 @@
         <v>94.5</v>
       </c>
       <c r="N15">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="O15">
+        <v>93.8</v>
+      </c>
+      <c r="P15">
+        <v>83.8</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>88.8</v>
+      </c>
+      <c r="S15">
         <v>96.3</v>
-      </c>
-      <c r="O15">
-        <v>90</v>
-      </c>
-      <c r="P15">
-        <v>78.8</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>86.5</v>
-      </c>
-      <c r="S15">
-        <v>94.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3543,22 +3516,22 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N16">
+        <v>95.3</v>
+      </c>
+      <c r="O16">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P16">
         <v>95</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>98.09999999999999</v>
-      </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S16">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3578,10 +3551,10 @@
         <v>50</v>
       </c>
       <c r="N17">
-        <v>91.3</v>
+        <v>64.8</v>
       </c>
       <c r="O17">
-        <v>50</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3625,22 +3598,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N18">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O18">
+        <v>95.3</v>
+      </c>
+      <c r="P18">
+        <v>85</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>95</v>
       </c>
-      <c r="P18">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
       <c r="S18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3696,10 +3669,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="S19">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3743,22 +3716,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N20">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="O20">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P20">
+        <v>96.3</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>96.3</v>
+      </c>
+      <c r="S20">
         <v>97.5</v>
-      </c>
-      <c r="O20">
-        <v>97.5</v>
-      </c>
-      <c r="P20">
-        <v>94.2</v>
-      </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
-        <v>96.2</v>
-      </c>
-      <c r="S20">
-        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3802,7 +3775,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3864,19 +3837,19 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P22">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="S22">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3920,22 +3893,22 @@
         <v>94.5</v>
       </c>
       <c r="N23">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P23">
-        <v>84.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3979,22 +3952,22 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N24">
+        <v>94.5</v>
+      </c>
+      <c r="O24">
+        <v>92.2</v>
+      </c>
+      <c r="P24">
+        <v>85</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>91.3</v>
       </c>
-      <c r="O24">
-        <v>90</v>
-      </c>
-      <c r="P24">
-        <v>80.8</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>88.5</v>
-      </c>
       <c r="S24">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4038,22 +4011,22 @@
         <v>98.2</v>
       </c>
       <c r="N25">
+        <v>99.2</v>
+      </c>
+      <c r="O25">
+        <v>93.8</v>
+      </c>
+      <c r="P25">
+        <v>88.8</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>92.5</v>
+      </c>
+      <c r="S25">
         <v>98.8</v>
-      </c>
-      <c r="O25">
-        <v>90</v>
-      </c>
-      <c r="P25">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>94.2</v>
-      </c>
-      <c r="S25">
-        <v>98.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4100,10 +4073,10 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P26">
-        <v>88.5</v>
+        <v>92.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4112,7 +4085,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4162,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4215,22 +4188,22 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N28">
+        <v>87.5</v>
+      </c>
+      <c r="O28">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P28">
+        <v>81.3</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>82.5</v>
       </c>
-      <c r="O28">
-        <v>85</v>
-      </c>
-      <c r="P28">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
-        <v>78.8</v>
-      </c>
       <c r="S28">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4274,22 +4247,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N29">
+        <v>92.2</v>
+      </c>
+      <c r="O29">
+        <v>93.8</v>
+      </c>
+      <c r="P29">
         <v>92.5</v>
       </c>
-      <c r="O29">
-        <v>92.5</v>
-      </c>
-      <c r="P29">
-        <v>94.2</v>
-      </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>92.3</v>
+        <v>91.3</v>
       </c>
       <c r="S29">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -4346,7 +4319,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4355,16 +4328,16 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>73.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="G2" s="2">
-        <v>26.9</v>
+        <v>11.5</v>
       </c>
       <c r="H2">
         <v>7.5</v>
@@ -4378,28 +4351,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3">
+        <v>26</v>
+      </c>
+      <c r="D3">
         <v>25</v>
       </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>96.2</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4413,22 +4386,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -4442,25 +4415,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>25</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -4474,28 +4447,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>7.7</v>
-      </c>
-      <c r="H6">
-        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4506,7 +4479,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -4515,19 +4488,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4577,7 +4550,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4609,19 +4582,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>50</v>
@@ -4632,19 +4605,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>20330051920132</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -4661,13 +4634,13 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>50</v>
@@ -4678,162 +4651,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920390</v>
+        <v>21330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920046</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920046</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920132</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920132</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920041</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920065</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
